--- a/UnityLoading/Assets/Data/Data.xlsx
+++ b/UnityLoading/Assets/Data/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityLoading\UnityLoading\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E29DA64-978A-47E0-B10E-8301A0ADBD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77CE853-D9A8-42EE-91A4-3B16E8D6FA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test" sheetId="1" r:id="rId1"/>
@@ -91,9 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>은하열차</t>
-  </si>
-  <si>
     <t>「개척」의 에이언즈 아키비리가 탑승했던 열차
 세계를 연결하는 철도를 따라 운행하며, 우주의 여러 세계를 거쳐갔다.</t>
   </si>
@@ -427,6 +424,10 @@
   </si>
   <si>
     <t>지오매로우</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>은하열차</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -858,16 +859,16 @@
         <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
@@ -881,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
       <c r="F2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
         <v>63</v>
-      </c>
-      <c r="G2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
@@ -904,16 +905,16 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" t="s">
         <v>65</v>
-      </c>
-      <c r="G3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
@@ -927,16 +928,16 @@
         <v>4</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
       <c r="F4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" t="s">
         <v>67</v>
-      </c>
-      <c r="G4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
@@ -950,16 +951,16 @@
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
       <c r="F5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" t="s">
         <v>69</v>
-      </c>
-      <c r="G5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
@@ -973,16 +974,16 @@
         <v>0</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
       <c r="F6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" t="s">
         <v>71</v>
-      </c>
-      <c r="G6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -996,16 +997,16 @@
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
       <c r="F7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" t="s">
         <v>73</v>
-      </c>
-      <c r="G7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
@@ -1019,16 +1020,16 @@
         <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
         <v>27</v>
       </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
       <c r="F8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" t="s">
         <v>75</v>
-      </c>
-      <c r="G8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
@@ -1042,16 +1043,16 @@
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
       <c r="F9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" t="s">
         <v>77</v>
-      </c>
-      <c r="G9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
@@ -1065,16 +1066,16 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
       <c r="F10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" t="s">
         <v>79</v>
-      </c>
-      <c r="G10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
@@ -1088,16 +1089,16 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="E11" t="s">
-        <v>34</v>
-      </c>
       <c r="F11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" t="s">
         <v>81</v>
-      </c>
-      <c r="G11" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
@@ -1111,16 +1112,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
       <c r="F12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" t="s">
         <v>83</v>
-      </c>
-      <c r="G12" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
@@ -1134,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
         <v>37</v>
       </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
       <c r="F13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" t="s">
         <v>85</v>
-      </c>
-      <c r="G13" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
@@ -1157,16 +1158,16 @@
         <v>0</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
         <v>39</v>
       </c>
-      <c r="E14" t="s">
-        <v>40</v>
-      </c>
       <c r="F14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" t="s">
         <v>87</v>
-      </c>
-      <c r="G14" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
@@ -1180,16 +1181,16 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" t="s">
         <v>41</v>
       </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
       <c r="F15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" t="s">
         <v>89</v>
-      </c>
-      <c r="G15" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
@@ -1203,16 +1204,16 @@
         <v>0</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" t="s">
         <v>43</v>
       </c>
-      <c r="E16" t="s">
-        <v>44</v>
-      </c>
       <c r="F16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" t="s">
         <v>91</v>
-      </c>
-      <c r="G16" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
@@ -1226,16 +1227,16 @@
         <v>0</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
         <v>45</v>
       </c>
-      <c r="E17" t="s">
-        <v>46</v>
-      </c>
       <c r="F17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" t="s">
         <v>93</v>
-      </c>
-      <c r="G17" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
@@ -1249,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
         <v>47</v>
       </c>
-      <c r="E18" t="s">
-        <v>48</v>
-      </c>
       <c r="F18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" t="s">
         <v>95</v>
-      </c>
-      <c r="G18" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
@@ -1272,16 +1273,16 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
         <v>49</v>
       </c>
-      <c r="E19" t="s">
-        <v>50</v>
-      </c>
       <c r="F19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" t="s">
         <v>97</v>
-      </c>
-      <c r="G19" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
@@ -1295,16 +1296,16 @@
         <v>0</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
         <v>51</v>
       </c>
-      <c r="E20" t="s">
-        <v>52</v>
-      </c>
       <c r="F20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" t="s">
         <v>99</v>
-      </c>
-      <c r="G20" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
@@ -1318,16 +1319,16 @@
         <v>0</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" t="s">
         <v>53</v>
       </c>
-      <c r="E21" t="s">
-        <v>54</v>
-      </c>
       <c r="F21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G21" t="s">
         <v>101</v>
-      </c>
-      <c r="G21" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
@@ -1341,16 +1342,16 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F22" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" t="s">
         <v>103</v>
-      </c>
-      <c r="G22" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
@@ -1364,16 +1365,16 @@
         <v>0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" t="s">
         <v>105</v>
-      </c>
-      <c r="G23" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
@@ -1387,16 +1388,16 @@
         <v>0</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" t="s">
         <v>57</v>
       </c>
-      <c r="E24" t="s">
-        <v>58</v>
-      </c>
       <c r="F24" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" t="s">
         <v>107</v>
-      </c>
-      <c r="G24" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
